--- a/data/trans_camb/IP16A05-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A05-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 14,63</t>
+          <t>-8,88; 16,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 33,24</t>
+          <t>-0,78; 35,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 20,44</t>
+          <t>-4,65; 21,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 25,03</t>
+          <t>-5,89; 28,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 18,19</t>
+          <t>-12,98; 18,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,4; 10,54</t>
+          <t>-15,82; 9,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 18,3</t>
+          <t>-4,28; 16,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 18,63</t>
+          <t>-4,48; 18,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 11,56</t>
+          <t>-7,44; 11,45</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-58,41; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-50,69; 903,23</t>
+          <t>-57,28; 583,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-51,75; 854,87</t>
+          <t>-57,95; 736,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-74,71; 556,03</t>
+          <t>-71,43; 568,96</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 36,84</t>
+          <t>1,71; 40,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-27,73; -3,15</t>
+          <t>-24,88; -3,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,39; 3,62</t>
+          <t>-20,42; 4,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-33,03; 5,99</t>
+          <t>-34,17; 6,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-27,52; 15,42</t>
+          <t>-25,74; 15,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-34,07; 0,17</t>
+          <t>-34,82; 1,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 21,82</t>
+          <t>-8,32; 20,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-19,54; 5,97</t>
+          <t>-18,98; 6,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-22,57; -1,54</t>
+          <t>-22,57; -0,62</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 1002,87</t>
+          <t>-11,8; 1278,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1014,32 +1014,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 258,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-85,93; 200,53</t>
+          <t>-82,95; 244,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 156,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-41,64; 279,46</t>
+          <t>-43,12; 211,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-86,65; 107,67</t>
+          <t>-86,42; 102,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-95,82; 19,67</t>
+          <t>-94,68; 16,47</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,93; 52,45</t>
+          <t>6,46; 50,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,3; 57,11</t>
+          <t>7,64; 57,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1124,32 +1124,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 28,12</t>
+          <t>-13,02; 30,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-28,06; -3,18</t>
+          <t>-27,36; -3,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-21,42; 7,99</t>
+          <t>-22,24; 7,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 29,36</t>
+          <t>-2,11; 28,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 20,9</t>
+          <t>-7,54; 20,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-15,12; 4,73</t>
+          <t>-14,4; 5,38</t>
         </is>
       </c>
     </row>
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 308,3</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-33,92; 919,06</t>
+          <t>-38,95; 982,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-72,41; 786,59</t>
+          <t>-72,51; 691,87</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 271,17</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 20,53</t>
+          <t>-8,06; 18,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,22; 8,32</t>
+          <t>-15,01; 8,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,42; 11,2</t>
+          <t>-18,96; 11,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,27; 9,48</t>
+          <t>-14,45; 9,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-17,29; 6,07</t>
+          <t>-17,38; 7,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-21,01; 2,01</t>
+          <t>-18,57; 2,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 10,28</t>
+          <t>-8,42; 9,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 3,66</t>
+          <t>-13,1; 3,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 4,01</t>
+          <t>-14,2; 2,97</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-43,79; 261,85</t>
+          <t>-39,2; 244,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-72,05; 118,49</t>
+          <t>-70,83; 124,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-84,6; 118,0</t>
+          <t>-82,28; 132,33</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-64,9; 138,19</t>
+          <t>-67,04; 145,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-85,4; 99,18</t>
+          <t>-82,61; 125,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-89,36; 45,15</t>
+          <t>-90,1; 70,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-40,17; 111,73</t>
+          <t>-42,72; 93,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-63,69; 37,27</t>
+          <t>-67,63; 44,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-77,08; 40,23</t>
+          <t>-75,03; 36,85</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 16,27</t>
+          <t>-12,22; 18,11</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 12,54</t>
+          <t>-14,1; 12,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-22,46; -0,29</t>
+          <t>-23,25; -0,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,62; 25,13</t>
+          <t>0,21; 25,52</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,21; 37,04</t>
+          <t>6,78; 37,35</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 7,53</t>
+          <t>-5,86; 7,21</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 16,98</t>
+          <t>-0,99; 16,77</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,8; 20,89</t>
+          <t>1,02; 20,16</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-10,53; 2,03</t>
+          <t>-9,94; 2,68</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-79,52; 542,89</t>
+          <t>-82,03; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-86,92; —</t>
+          <t>-90,63; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-33,45; 909,28</t>
+          <t>-32,85; 819,28</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-19,21; 875,63</t>
+          <t>-8,44; 1117,17</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 232,91</t>
+          <t>-100,0; 291,15</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,48</t>
+          <t>0,0; 43,01</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,32</t>
+          <t>0,0; 22,23</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4,61; 42,47</t>
+          <t>4,83; 41,88</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,89</t>
+          <t>0,0; 29,9</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,77</t>
+          <t>0,0; 38,29</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,33</t>
+          <t>0,0; 28,37</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,01; 27,5</t>
+          <t>2,97; 24,49</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2,43; 21,91</t>
+          <t>2,41; 20,77</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4,41; 26,49</t>
+          <t>4,56; 24,54</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,27; 15,58</t>
+          <t>1,56; 15,6</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 8,35</t>
+          <t>-3,67; 8,61</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 6,03</t>
+          <t>-7,11; 5,87</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 8,99</t>
+          <t>-4,18; 8,13</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 8,89</t>
+          <t>-3,74; 8,99</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 0,04</t>
+          <t>-10,52; -0,06</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,24; 10,15</t>
+          <t>1,15; 10,41</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 6,19</t>
+          <t>-2,48; 6,34</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 0,96</t>
+          <t>-6,97; 1,43</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>15,19; 261,25</t>
+          <t>9,02; 268,53</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-37,65; 150,24</t>
+          <t>-32,17; 147,72</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-53,77; 105,8</t>
+          <t>-58,38; 89,7</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-29,74; 116,11</t>
+          <t>-33,29; 97,24</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-35,31; 108,83</t>
+          <t>-28,68; 109,87</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-76,11; 2,65</t>
+          <t>-75,2; 3,18</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,39; 135,07</t>
+          <t>8,18; 129,42</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-22,3; 74,55</t>
+          <t>-20,97; 80,65</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-59,47; 12,45</t>
+          <t>-56,78; 22,39</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A05-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A05-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 16,44</t>
+          <t>-11,85; 14,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 35,23</t>
+          <t>-2,35; 32,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 21,07</t>
+          <t>-5,86; 20,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 28,3</t>
+          <t>-7,1; 26,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 18,49</t>
+          <t>-12,18; 18,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,82; 9,33</t>
+          <t>-16,53; 9,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 16,83</t>
+          <t>-5,26; 15,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 18,03</t>
+          <t>-4,28; 18,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 11,45</t>
+          <t>-8,05; 10,42</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-55,1; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-57,28; 583,11</t>
+          <t>-54,45; 617,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-57,95; 736,71</t>
+          <t>-53,71; 774,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-71,43; 568,96</t>
+          <t>-71,33; 524,52</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 40,0</t>
+          <t>0,63; 36,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-24,88; -3,14</t>
+          <t>-27,43; -3,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,42; 4,25</t>
+          <t>-20,48; 4,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-34,17; 6,36</t>
+          <t>-34,37; 5,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-25,74; 15,68</t>
+          <t>-26,96; 14,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-34,82; 1,92</t>
+          <t>-35,73; -1,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 20,11</t>
+          <t>-8,68; 20,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-18,98; 6,73</t>
+          <t>-18,7; 6,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-22,57; -0,62</t>
+          <t>-22,53; -0,95</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,8; 1278,91</t>
+          <t>-25,93; 1125,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-82,95; 244,33</t>
+          <t>-86,51; 151,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-43,12; 211,51</t>
+          <t>-44,6; 222,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-86,42; 102,15</t>
+          <t>-85,5; 89,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-94,68; 16,47</t>
+          <t>-95,94; 58,21</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,46; 50,81</t>
+          <t>7,17; 53,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,64; 57,66</t>
+          <t>8,0; 56,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1124,32 +1124,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,02; 30,14</t>
+          <t>-13,42; 28,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-27,36; -3,06</t>
+          <t>-27,29; -3,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-22,24; 7,66</t>
+          <t>-22,04; 8,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 28,92</t>
+          <t>-1,94; 29,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 20,81</t>
+          <t>-9,07; 20,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 5,38</t>
+          <t>-14,68; 5,63</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 641,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,17 +1240,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 308,3</t>
+          <t>-100,0; 304,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-38,95; 982,12</t>
+          <t>-29,05; 1119,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-72,51; 691,87</t>
+          <t>-78,75; 786,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 18,55</t>
+          <t>-7,24; 19,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,01; 8,63</t>
+          <t>-14,69; 8,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,96; 11,4</t>
+          <t>-18,82; 12,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 9,68</t>
+          <t>-14,54; 9,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-17,38; 7,46</t>
+          <t>-17,96; 6,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 2,92</t>
+          <t>-19,1; 2,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 9,5</t>
+          <t>-7,66; 10,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 3,89</t>
+          <t>-11,54; 4,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-14,2; 2,97</t>
+          <t>-15,79; 3,54</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-39,2; 244,42</t>
+          <t>-38,94; 256,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-70,83; 124,04</t>
+          <t>-70,35; 127,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-82,28; 132,33</t>
+          <t>-81,71; 130,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-67,04; 145,12</t>
+          <t>-68,49; 139,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-82,61; 125,78</t>
+          <t>-83,82; 133,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-90,1; 70,86</t>
+          <t>-90,07; 80,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-42,72; 93,84</t>
+          <t>-40,24; 106,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-67,63; 44,23</t>
+          <t>-61,96; 60,26</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-75,03; 36,85</t>
+          <t>-79,05; 39,91</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 18,11</t>
+          <t>-10,78; 18,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,1; 12,92</t>
+          <t>-14,1; 14,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-23,25; -0,02</t>
+          <t>-22,09; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,21; 25,52</t>
+          <t>0,15; 22,71</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,78; 37,35</t>
+          <t>7,97; 38,82</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 7,21</t>
+          <t>-6,16; 7,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 16,77</t>
+          <t>-1,77; 16,65</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,02; 20,16</t>
+          <t>0,54; 20,83</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-9,94; 2,68</t>
+          <t>-11,01; 2,16</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-82,03; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-90,63; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-32,85; 819,28</t>
+          <t>-46,2; 807,25</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 1117,17</t>
+          <t>-15,3; 1155,33</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 291,15</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,01</t>
+          <t>0,0; 42,97</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,23</t>
+          <t>0,0; 23,06</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4,83; 41,88</t>
+          <t>4,77; 39,67</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,9</t>
+          <t>0,0; 29,83</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,29</t>
+          <t>0,0; 39,68</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,37</t>
+          <t>0,0; 27,64</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,97; 24,49</t>
+          <t>3,04; 26,72</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2,41; 20,77</t>
+          <t>2,44; 19,22</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4,56; 24,54</t>
+          <t>3,41; 25,91</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,56; 15,6</t>
+          <t>2,19; 15,99</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 8,61</t>
+          <t>-4,01; 8,43</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 5,87</t>
+          <t>-7,0; 6,68</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 8,13</t>
+          <t>-3,64; 8,6</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 8,99</t>
+          <t>-4,91; 8,56</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-10,52; -0,06</t>
+          <t>-10,47; -0,43</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,15; 10,41</t>
+          <t>0,91; 10,16</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 6,34</t>
+          <t>-2,24; 6,65</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 1,43</t>
+          <t>-7,36; 1,45</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>9,02; 268,53</t>
+          <t>10,88; 291,83</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-32,17; 147,72</t>
+          <t>-33,48; 152,13</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-58,38; 89,7</t>
+          <t>-59,69; 110,54</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-33,29; 97,24</t>
+          <t>-27,98; 109,93</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-28,68; 109,87</t>
+          <t>-36,81; 101,06</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-75,2; 3,18</t>
+          <t>-76,81; -2,03</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,18; 129,42</t>
+          <t>7,93; 129,01</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-20,97; 80,65</t>
+          <t>-18,68; 85,38</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-56,78; 22,39</t>
+          <t>-61,26; 18,94</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A05-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A05-Clase-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos antibióticos</t>
+          <t>Menores que consumieron medicamentos antibióticos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8,31</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,02</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-3,18</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>3,04</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>13,6</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8,21</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8,31</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,02</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-3,08</t>
+          <t>7,43</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,77</t>
+          <t>1,48</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 14,59</t>
+          <t>-6,58; 25,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 32,94</t>
+          <t>-14,44; 18,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 20,46</t>
+          <t>-16,52; 10,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 26,1</t>
+          <t>-8,77; 14,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 18,64</t>
+          <t>-3,3; 33,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,53; 9,17</t>
+          <t>-6,3; 18,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 15,88</t>
+          <t>-4,28; 18,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 18,86</t>
+          <t>-5,16; 18,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 10,42</t>
+          <t>-7,56; 11,18</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>90,96%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-0,18%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-34,81%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>73,64%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>329,33%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>198,86%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>90,96%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-0,18%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-33,71%</t>
+          <t>179,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-58,41; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-55,1; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-54,45; 617,82</t>
+          <t>-50,69; 903,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-53,71; 774,79</t>
+          <t>-51,75; 854,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-71,33; 524,52</t>
+          <t>-74,96; 538,84</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-14,83</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-6,99</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-17,51</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>18,75</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-10,07</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-5,97</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-14,83</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-6,99</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-17,33</t>
+          <t>-6,26</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-11,4</t>
+          <t>-11,64</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 36,66</t>
+          <t>-33,03; 5,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-27,43; -3,12</t>
+          <t>-27,52; 15,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,48; 4,01</t>
+          <t>-34,19; 0,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-34,37; 5,74</t>
+          <t>1,37; 36,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-26,96; 14,02</t>
+          <t>-27,73; -3,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,73; -1,22</t>
+          <t>-20,71; 3,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 20,57</t>
+          <t>-8,23; 21,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-18,7; 6,19</t>
+          <t>-19,54; 5,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-22,53; -0,95</t>
+          <t>-22,84; -1,96</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-68,12%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-32,11%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-80,43%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>186,32%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-59,29%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-68,12%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-32,11%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-79,57%</t>
+          <t>-62,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-72,74%</t>
+          <t>-74,27%</t>
         </is>
       </c>
     </row>
@@ -999,27 +999,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,93; 1125,13</t>
+          <t>-100,0; 258,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-85,93; 200,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 146,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-14,46; 1002,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-86,51; 151,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-44,6; 222,6</t>
+          <t>-41,64; 279,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-85,5; 89,34</t>
+          <t>-86,65; 107,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-95,94; 58,21</t>
+          <t>-96,32; 13,66</t>
         </is>
       </c>
     </row>
@@ -1056,34 +1056,34 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,78</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-12,31</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-6,27</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>24,75</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>28,07</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,78</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-12,31</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-5,96</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
           <t>12,59</t>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-4,09</t>
+          <t>-4,47</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,17; 53,87</t>
+          <t>-12,93; 28,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,0; 56,86</t>
+          <t>-28,06; -3,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-22,19; 6,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 28,2</t>
+          <t>7,93; 52,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-27,29; -3,16</t>
+          <t>7,3; 57,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-22,04; 8,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 29,89</t>
+          <t>-2,1; 29,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 20,57</t>
+          <t>-7,32; 20,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,68; 5,63</t>
+          <t>-16,32; 3,62</t>
         </is>
       </c>
     </row>
@@ -1162,34 +1162,34 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>38,8%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-50,92%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>38,8%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-48,43%</t>
-        </is>
-      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t>153,99%</t>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-50,05%</t>
+          <t>-54,75%</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 641,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 304,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-29,05; 1119,36</t>
+          <t>-33,92; 919,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-78,75; 786,9</t>
+          <t>-72,41; 786,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 279,3</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-1,46</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-5,02</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-7,7</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>5,51</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-2,87</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-3,53</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,46</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-5,02</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-7,9</t>
+          <t>-1,0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-5,37</t>
+          <t>-4,61</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 19,13</t>
+          <t>-14,27; 9,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,69; 8,99</t>
+          <t>-17,29; 6,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,82; 12,31</t>
+          <t>-20,79; 2,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,54; 9,76</t>
+          <t>-8,48; 20,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-17,96; 6,99</t>
+          <t>-16,22; 8,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,1; 2,19</t>
+          <t>-14,26; 11,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 10,34</t>
+          <t>-7,26; 10,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 4,98</t>
+          <t>-11,77; 3,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-15,79; 3,54</t>
+          <t>-12,75; 3,54</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-10,23%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-35,25%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-54,01%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>38,45%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-20,04%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-24,64%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-10,23%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-35,25%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-55,43%</t>
+          <t>-6,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-37,56%</t>
+          <t>-32,26%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-38,94; 256,83</t>
+          <t>-64,9; 138,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-70,35; 127,61</t>
+          <t>-85,4; 99,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-81,71; 130,48</t>
+          <t>-89,41; 53,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-68,49; 139,33</t>
+          <t>-43,79; 261,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-83,82; 133,05</t>
+          <t>-72,05; 118,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-90,07; 80,87</t>
+          <t>-65,7; 183,95</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-40,24; 106,72</t>
+          <t>-40,17; 111,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-61,96; 60,26</t>
+          <t>-63,69; 37,27</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-79,05; 39,91</t>
+          <t>-67,13; 36,13</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>10,72</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>20,56</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,17</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>3,32</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0,08</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-8,23</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>10,72</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>20,56</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,21</t>
+          <t>-8,39</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,96</t>
+          <t>-3,12</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 18,58</t>
+          <t>0,62; 25,13</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,1; 14,27</t>
+          <t>8,21; 37,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-22,09; 0,0</t>
+          <t>-7,59; 7,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,15; 22,71</t>
+          <t>-12,01; 16,27</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,97; 38,82</t>
+          <t>-15,07; 12,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 7,26</t>
+          <t>-22,5; -0,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 16,65</t>
+          <t>-2,1; 16,98</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,54; 20,83</t>
+          <t>0,8; 20,89</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 2,16</t>
+          <t>-10,66; 1,77</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>425,18%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>815,98%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>46,45%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>34,64%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>0,88%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-85,88%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>425,18%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>815,98%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>-87,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-52,54%</t>
+          <t>-55,39%</t>
         </is>
       </c>
     </row>
@@ -1662,12 +1662,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-79,52; 542,89</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-86,92; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-46,2; 807,25</t>
+          <t>-33,45; 909,28</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-15,3; 1155,33</t>
+          <t>-19,21; 875,63</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 289,67</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>9,71</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>12,37</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>6,35</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>10,89</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>4,33</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>19,13</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>9,71</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>12,37</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,64</t>
+          <t>17,44</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11,63</t>
+          <t>11,55</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,97</t>
+          <t>0,0; 33,89</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,06</t>
+          <t>0,0; 44,77</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4,77; 39,67</t>
+          <t>0,0; 26,08</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,83</t>
+          <t>0,0; 52,48</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,68</t>
+          <t>0,0; 24,32</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,64</t>
+          <t>4,17; 39,76</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,04; 26,72</t>
+          <t>3,01; 27,5</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2,44; 19,22</t>
+          <t>2,43; 21,91</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3,41; 25,91</t>
+          <t>4,47; 26,29</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>2,32</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>1,76</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-5,35</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>9,02</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>2,28</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-0,36</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>2,32</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>1,76</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-5,39</t>
+          <t>-0,46</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-2,99</t>
+          <t>-3,11</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,19; 15,99</t>
+          <t>-4,24; 8,99</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 8,43</t>
+          <t>-4,71; 8,89</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 6,68</t>
+          <t>-10,57; 0,05</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 8,6</t>
+          <t>2,27; 15,58</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 8,56</t>
+          <t>-4,32; 8,35</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-10,47; -0,43</t>
+          <t>-6,11; 5,13</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,91; 10,16</t>
+          <t>1,24; 10,15</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 6,65</t>
+          <t>-2,6; 6,19</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 1,45</t>
+          <t>-7,16; 0,34</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>21,33%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>16,18%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-49,34%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>101,11%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>25,54%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-4,09%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>21,33%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>16,18%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-49,64%</t>
+          <t>-5,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-29,97%</t>
+          <t>-31,18%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>10,88; 291,83</t>
+          <t>-29,74; 116,11</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-33,48; 152,13</t>
+          <t>-35,31; 108,83</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-59,69; 110,54</t>
+          <t>-74,76; 8,05</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-27,98; 109,93</t>
+          <t>15,19; 261,25</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-36,81; 101,06</t>
+          <t>-37,65; 150,24</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-76,81; -2,03</t>
+          <t>-50,08; 89,78</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,93; 129,01</t>
+          <t>9,39; 135,07</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-18,68; 85,38</t>
+          <t>-22,3; 74,55</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-61,26; 18,94</t>
+          <t>-58,29; 5,37</t>
         </is>
       </c>
     </row>
